--- a/4.zadatak.xlsx
+++ b/4.zadatak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DT User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1E180C-6B79-41BC-A286-C27CBE26F54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8405AA6C-19F0-4586-8B9B-462E97C3E9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="14292" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Defect Tracking Log" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="100">
   <si>
     <r>
       <rPr>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t>Post-Deployment</t>
-  </si>
-  <si>
-    <t>Defect Tracking Log Instructions</t>
   </si>
   <si>
     <t>Field</t>
@@ -551,6 +548,66 @@
   <si>
     <t>Amina Gutošić, Nejla Čajdin, Hasna Bunar</t>
   </si>
+  <si>
+    <t xml:space="preserve">Amina Gutošić, Nejla Čajdin, Hasna Bunar </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>4-6 Hours</t>
+  </si>
+  <si>
+    <t>5-8 Hours</t>
+  </si>
+  <si>
+    <t>3-5 Hours</t>
+  </si>
+  <si>
+    <t>8-12 Hours</t>
+  </si>
+  <si>
+    <t>6-8 Hours</t>
+  </si>
+  <si>
+    <t>6.1.2026.</t>
+  </si>
+  <si>
+    <t>3.1.2026.</t>
+  </si>
+  <si>
+    <t>2.1.2026.</t>
+  </si>
+  <si>
+    <t>Correct the logic that updates the total number of ratings on the user profile to ensure that a removed rating is properly deducted from the total count. Review and adjust the backend logic handling rating counter updates to maintain consistency when adding or removing ratings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad code </t>
+  </si>
+  <si>
+    <t>Implement input validation to ensure that the selected reading start date cannot be earlier than the book’s publishing date. Add logic to validate the dates both on the client side (UI) and server side, and display an error message if the condition is violated.</t>
+  </si>
+  <si>
+    <t>Oversight</t>
+  </si>
+  <si>
+    <t>Update the logic responsible for calculating and displaying the number of reviews under the user’s profile picture on the Book Details page. Ensure that the review count is correctly incremented and that it synchronizes with the actual number of posted reviews.</t>
+  </si>
+  <si>
+    <t>Investigate the backend handling for the "Create a Group" functionality to identify why the request fails despite providing valid inputs. Fix any issues in the group creation API or server logic, ensuring valid requests are processed and groups are successfully created.</t>
+  </si>
+  <si>
+    <t>Fix the logic that fetches and displays the list of discussion topics on the Discussions page. Ensure the newly created topics are correctly saved in the backend and retrieved/displayed in the Discussions list. Validate that the topic list updates dynamically or upon page refresh.</t>
+  </si>
+  <si>
+    <t>Investigate the backend logic responsible for calculating the number of books in each bookshelf category. Fix any discrepancies in the categorization or counting mechanism to ensure accurate and consistent data is displayed for all categories. Perform database checks to verify data integrity and test the updates thoroughly.</t>
+  </si>
+  <si>
+    <t>Add validation to the "Date started" field to ensure that the entered date cannot precede the user's birth year. Implement this validation both on the client (UI) side for immediate feedback and on the server side to prevent invalid data from being submitted.</t>
+  </si>
+  <si>
+    <t>godreads</t>
+  </si>
 </sst>
 </file>
 
@@ -559,7 +616,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -621,6 +678,27 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -959,14 +1037,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -979,17 +1066,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1046,10 +1127,66 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="10" xr:uid="{5654359E-6D6C-4AB6-837E-A447C7EE3EC5}"/>
+    <cellStyle name="Normal 11" xfId="11" xr:uid="{E8D45EF1-59C4-4C04-BBC8-1B706FA220DA}"/>
+    <cellStyle name="Normal 12" xfId="2" xr:uid="{A23021DE-04D5-45B6-9905-A10D694CAB55}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A36E087D-E5D2-43A8-8892-87B9148CC47A}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{19C1034D-5DF6-464F-9DAC-7EEAB2F204EF}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{06428994-D189-4D12-81AB-B18CF3E20642}"/>
+    <cellStyle name="Normal 5" xfId="5" xr:uid="{5BD26EEF-1020-4DED-9AEB-BCABF196EC9F}"/>
+    <cellStyle name="Normal 6" xfId="6" xr:uid="{05E3A5CD-4D92-4AC7-B1E6-77711045430B}"/>
+    <cellStyle name="Normal 7" xfId="7" xr:uid="{D19A9691-8EF9-4482-AE2F-E1EB002533F6}"/>
+    <cellStyle name="Normal 8" xfId="8" xr:uid="{E10DF1D4-96CE-4F32-A900-6B636C5DC01C}"/>
+    <cellStyle name="Normal 9" xfId="9" xr:uid="{4B7DE7B0-6C6E-420E-AB40-49AA1D01EFFF}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1266,20 +1403,20 @@
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.28515625" customWidth="1"/>
     <col min="4" max="4" width="60.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="38.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="48.5703125" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="12" max="12" width="63.5703125" customWidth="1"/>
     <col min="13" max="13" width="12.85546875" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" customWidth="1"/>
     <col min="16" max="16" width="11.42578125" customWidth="1"/>
     <col min="17" max="18" width="8" customWidth="1"/>
     <col min="19" max="19" width="8" hidden="1" customWidth="1"/>
@@ -1288,618 +1425,764 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="3"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
     </row>
     <row r="9" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:24" ht="33.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="T10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="V10" s="8" t="s">
+      <c r="V10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="W10" s="8" t="s">
+      <c r="W10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="X10" s="8" t="s">
+      <c r="X10" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="306" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="38">
         <v>1</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="O11" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="318.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="39">
+        <v>2</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D12" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="E12" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="O12" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="X12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="318.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="39">
+        <v>3</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11" t="s">
+      <c r="E13" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="12"/>
-      <c r="T11" s="8" t="s">
+      <c r="L13" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="M13" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="O13" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="318.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="39">
+        <v>4</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="36" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" ht="318.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="13">
-        <v>2</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="L14" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="N14" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="T14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="V14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="X14" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="395.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="39">
+        <v>5</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="K15" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="N15" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="O15" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="259.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="39">
+        <v>6</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="K16" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="N16" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="O16" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="300.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="39">
+        <v>7</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
+      <c r="J17" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="16"/>
-      <c r="T12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="V12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="W12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="X12" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="306" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
-        <v>3</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="16"/>
-      <c r="T13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="V13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="W13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="X13" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="318.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="13">
-        <v>4</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="16"/>
-      <c r="T14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="V14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="W14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="X14" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="395.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="13">
-        <v>5</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="L17" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="M17" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="16"/>
-      <c r="W15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="X15" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="259.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
-        <v>6</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="16"/>
-      <c r="W16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="X16" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="300.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
-        <v>7</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="16"/>
-      <c r="X17" s="8" t="s">
+      <c r="N17" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="O17" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="X17" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13">
+      <c r="A18" s="39">
         <v>8</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="16"/>
-      <c r="X18" s="8" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="10"/>
+      <c r="X18" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13">
+      <c r="A19" s="39">
         <v>9</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="16"/>
-      <c r="X19" s="8" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="10"/>
+      <c r="X19" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
+      <c r="A20" s="39">
         <v>10</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="16"/>
-      <c r="X20" s="8" t="s">
+      <c r="B20" s="8"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="10"/>
+      <c r="X20" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="13">
+      <c r="A21" s="39">
         <v>11</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="16"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="10"/>
     </row>
     <row r="22" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13">
+      <c r="A22" s="39">
         <v>12</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="16"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="10"/>
     </row>
     <row r="23" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="13">
+      <c r="A23" s="39">
         <v>13</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="16"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="10"/>
     </row>
     <row r="24" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13">
+      <c r="A24" s="39">
         <v>14</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="16"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="10"/>
     </row>
     <row r="25" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13">
+      <c r="A25" s="39">
         <v>15</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="16"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
+      <c r="A26" s="39">
         <v>16</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="16"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="10"/>
     </row>
     <row r="27" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13">
+      <c r="A27" s="39">
         <v>17</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="16"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="10"/>
     </row>
     <row r="28" spans="1:24" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+      <c r="A28" s="40">
         <v>18</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="21"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="14"/>
     </row>
     <row r="29" spans="1:24" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2880,7 +3163,7 @@
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt=" - " sqref="E11:E28" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt=" - " sqref="E18:E28" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>PM</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt=" - " sqref="G11:G28" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -2913,160 +3196,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
-        <v>42</v>
+      <c r="A1" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="24" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="B4" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="26" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="28" t="s">
+    <row r="6" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="28" t="s">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="28" t="s">
+    <row r="8" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="28" t="s">
+    <row r="9" spans="1:2" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="28" t="s">
+    <row r="10" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="29" t="s">
+    <row r="11" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="33"/>
+      <c r="B11" s="23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40"/>
-      <c r="B11" s="30" t="s">
+    <row r="12" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="33"/>
+      <c r="B12" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="40"/>
-      <c r="B12" s="30" t="s">
+    <row r="13" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="34"/>
+      <c r="B13" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="41"/>
-      <c r="B13" s="30" t="s">
+    <row r="14" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="28" t="s">
+    <row r="15" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="28" t="s">
+    <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
+      <c r="B16" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="28" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="28" t="s">
+    <row r="18" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27" t="s">
+      <c r="B18" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="28" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="28" t="s">
+    <row r="20" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="28" t="s">
+    <row r="21" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31" t="s">
+      <c r="B21" s="25" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
+      <c r="A23" s="2"/>
     </row>
     <row r="24" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
